--- a/countries/cn-xj/2000-2004.xlsx
+++ b/countries/cn-xj/2000-2004.xlsx
@@ -765,9 +765,12 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1150,9 +1153,12 @@
       <c r="O4" t="n">
         <v>181</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.9220580743759551</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1535,9 +1541,12 @@
       <c r="O6" t="n">
         <v>1270</v>
       </c>
+      <c r="R6" t="n">
+        <v>6.469689251146205</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1920,9 +1929,12 @@
       <c r="O8" t="n">
         <v>57</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.2903718797758533</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2305,9 +2317,12 @@
       <c r="O10" t="n">
         <v>6</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.03056546102903719</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2690,9 +2705,12 @@
       <c r="O12" t="n">
         <v>232</v>
       </c>
+      <c r="R12" t="n">
+        <v>1.181864493122771</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -3075,9 +3093,12 @@
       <c r="O14" t="n">
         <v>2990</v>
       </c>
+      <c r="R14" t="n">
+        <v>15.2317880794702</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -3460,9 +3481,12 @@
       <c r="O16" t="n">
         <v>30</v>
       </c>
+      <c r="R16" t="n">
+        <v>0.1528273051451859</v>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -3845,9 +3869,12 @@
       <c r="O18" t="n">
         <v>41</v>
       </c>
+      <c r="R18" t="n">
+        <v>0.2088639836984208</v>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -4230,9 +4257,12 @@
       <c r="O20" t="n">
         <v>15</v>
       </c>
+      <c r="R20" t="n">
+        <v>0.07641365257259297</v>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -4615,9 +4645,12 @@
       <c r="O22" t="n">
         <v>12</v>
       </c>
+      <c r="R22" t="n">
+        <v>0.06113092205807438</v>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -5000,9 +5033,12 @@
       <c r="O24" t="n">
         <v>123</v>
       </c>
+      <c r="R24" t="n">
+        <v>0.6265919510952623</v>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -5385,9 +5421,12 @@
       <c r="O26" t="n">
         <v>63</v>
       </c>
+      <c r="R26" t="n">
+        <v>0.3209373408048904</v>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -5770,9 +5809,12 @@
       <c r="O28" t="n">
         <v>200</v>
       </c>
+      <c r="R28" t="n">
+        <v>1.018848700967906</v>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -6155,9 +6197,12 @@
       <c r="O30" t="n">
         <v>16</v>
       </c>
+      <c r="R30" t="n">
+        <v>0.0815078960774325</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -6540,9 +6585,12 @@
       <c r="O32" t="n">
         <v>4</v>
       </c>
+      <c r="R32" t="n">
+        <v>0.02037697401935813</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -6925,9 +6973,12 @@
       <c r="O34" t="n">
         <v>9</v>
       </c>
+      <c r="R34" t="n">
+        <v>0.04584819154355578</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -7310,9 +7361,12 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
+      <c r="R36" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -7695,9 +7749,12 @@
       <c r="O38" t="n">
         <v>215</v>
       </c>
+      <c r="R38" t="n">
+        <v>1.095262353540499</v>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -8080,9 +8137,12 @@
       <c r="O40" t="n">
         <v>1483</v>
       </c>
+      <c r="R40" t="n">
+        <v>7.554763117677025</v>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -8465,9 +8525,12 @@
       <c r="O42" t="n">
         <v>60</v>
       </c>
+      <c r="R42" t="n">
+        <v>0.3056546102903719</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -8850,9 +8913,12 @@
       <c r="O44" t="n">
         <v>11</v>
       </c>
+      <c r="R44" t="n">
+        <v>0.05603667855323484</v>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -9235,9 +9301,12 @@
       <c r="O46" t="n">
         <v>232</v>
       </c>
+      <c r="R46" t="n">
+        <v>1.181864493122771</v>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -9620,9 +9689,12 @@
       <c r="O48" t="n">
         <v>2649</v>
       </c>
+      <c r="R48" t="n">
+        <v>13.49465104431992</v>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -10005,9 +10077,12 @@
       <c r="O50" t="n">
         <v>57</v>
       </c>
+      <c r="R50" t="n">
+        <v>0.2903718797758533</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -10390,9 +10465,12 @@
       <c r="O52" t="n">
         <v>68</v>
       </c>
+      <c r="R52" t="n">
+        <v>0.3464085583290881</v>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10775,9 +10853,12 @@
       <c r="O54" t="n">
         <v>17</v>
       </c>
+      <c r="R54" t="n">
+        <v>0.08660213958227203</v>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11160,9 +11241,12 @@
       <c r="O56" t="n">
         <v>14</v>
       </c>
+      <c r="R56" t="n">
+        <v>0.07131940906775344</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -11545,9 +11629,12 @@
       <c r="O58" t="n">
         <v>208</v>
       </c>
+      <c r="R58" t="n">
+        <v>1.059602649006623</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11930,9 +12017,12 @@
       <c r="O60" t="n">
         <v>64</v>
       </c>
+      <c r="R60" t="n">
+        <v>0.32603158430973</v>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12315,9 +12405,12 @@
       <c r="O62" t="n">
         <v>346</v>
       </c>
+      <c r="R62" t="n">
+        <v>1.762608252674478</v>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12700,9 +12793,12 @@
       <c r="O64" t="n">
         <v>51</v>
       </c>
+      <c r="R64" t="n">
+        <v>0.2598064187468161</v>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -13085,9 +13181,12 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
+      <c r="R66" t="n">
+        <v>0.02037697401935813</v>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13470,9 +13569,12 @@
       <c r="O68" t="n">
         <v>6</v>
       </c>
+      <c r="R68" t="n">
+        <v>0.03056546102903719</v>
+      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -13855,9 +13957,12 @@
       <c r="O70" t="n">
         <v>51</v>
       </c>
+      <c r="R70" t="n">
+        <v>0.2598064187468161</v>
+      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -14240,9 +14345,12 @@
       <c r="O72" t="n">
         <v>4</v>
       </c>
+      <c r="R72" t="n">
+        <v>0.02037697401935813</v>
+      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -14625,9 +14733,12 @@
       <c r="O74" t="n">
         <v>257</v>
       </c>
+      <c r="R74" t="n">
+        <v>1.30922058074376</v>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -15010,9 +15121,12 @@
       <c r="O76" t="n">
         <v>1998</v>
       </c>
+      <c r="R76" t="n">
+        <v>10.17829852266938</v>
+      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -15395,9 +15509,12 @@
       <c r="O78" t="n">
         <v>92</v>
       </c>
+      <c r="R78" t="n">
+        <v>0.4686704024452369</v>
+      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -15780,9 +15897,12 @@
       <c r="O80" t="n">
         <v>5</v>
       </c>
+      <c r="R80" t="n">
+        <v>0.02547121752419765</v>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -16165,9 +16285,12 @@
       <c r="O82" t="n">
         <v>384</v>
       </c>
+      <c r="R82" t="n">
+        <v>1.95618950585838</v>
+      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -16550,9 +16673,12 @@
       <c r="O84" t="n">
         <v>3355</v>
       </c>
+      <c r="R84" t="n">
+        <v>17.09118695873663</v>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -16935,9 +17061,12 @@
       <c r="O86" t="n">
         <v>57</v>
       </c>
+      <c r="R86" t="n">
+        <v>0.2903718797758533</v>
+      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -17320,9 +17449,12 @@
       <c r="O88" t="n">
         <v>91</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.4635761589403974</v>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -17705,9 +17837,12 @@
       <c r="O90" t="n">
         <v>107</v>
       </c>
+      <c r="R90" t="n">
+        <v>0.5450840550178299</v>
+      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -18090,9 +18225,12 @@
       <c r="O92" t="n">
         <v>20</v>
       </c>
+      <c r="R92" t="n">
+        <v>0.1018848700967906</v>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -18475,9 +18613,12 @@
       <c r="O94" t="n">
         <v>258</v>
       </c>
+      <c r="R94" t="n">
+        <v>1.314314824248599</v>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -18860,9 +19001,12 @@
       <c r="O96" t="n">
         <v>86</v>
       </c>
+      <c r="R96" t="n">
+        <v>0.4381049414161997</v>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -19245,9 +19389,12 @@
       <c r="O98" t="n">
         <v>1348</v>
       </c>
+      <c r="R98" t="n">
+        <v>6.867040244523688</v>
+      </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -19630,9 +19777,12 @@
       <c r="O100" t="n">
         <v>106</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.5399898115129903</v>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -20015,9 +20165,12 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
+      <c r="R102" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -20400,9 +20553,12 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="R104" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -20785,9 +20941,12 @@
       <c r="O106" t="n">
         <v>19</v>
       </c>
+      <c r="R106" t="n">
+        <v>0.09679062659195109</v>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -21170,9 +21329,12 @@
       <c r="O108" t="n">
         <v>139</v>
       </c>
+      <c r="R108" t="n">
+        <v>0.7080998471726949</v>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -21555,9 +21717,12 @@
       <c r="O110" t="n">
         <v>2</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -21940,9 +22105,12 @@
       <c r="O112" t="n">
         <v>219</v>
       </c>
+      <c r="R112" t="n">
+        <v>1.115639327559858</v>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -22325,9 +22493,12 @@
       <c r="O114" t="n">
         <v>1981</v>
       </c>
+      <c r="R114" t="n">
+        <v>10.09169638308711</v>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -22710,9 +22881,12 @@
       <c r="O116" t="n">
         <v>82</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.4177279673968415</v>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -23095,9 +23269,12 @@
       <c r="O118" t="n">
         <v>13</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.06622516556291391</v>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -23480,9 +23657,12 @@
       <c r="O120" t="n">
         <v>534</v>
       </c>
+      <c r="R120" t="n">
+        <v>2.72032603158431</v>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -23865,9 +24045,12 @@
       <c r="O122" t="n">
         <v>2893</v>
       </c>
+      <c r="R122" t="n">
+        <v>14.73764645950077</v>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -24250,9 +24433,12 @@
       <c r="O124" t="n">
         <v>62</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.3158430973000509</v>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -24635,9 +24821,12 @@
       <c r="O126" t="n">
         <v>69</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.3515028018339276</v>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -25020,9 +25209,12 @@
       <c r="O128" t="n">
         <v>122</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.6214977075904229</v>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -25405,9 +25597,12 @@
       <c r="O130" t="n">
         <v>61</v>
       </c>
+      <c r="R130" t="n">
+        <v>0.3107488537952114</v>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -25790,9 +25985,12 @@
       <c r="O132" t="n">
         <v>273</v>
       </c>
+      <c r="R132" t="n">
+        <v>1.390728476821192</v>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -26175,9 +26373,12 @@
       <c r="O134" t="n">
         <v>84</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.4279164544065206</v>
+      </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -26560,9 +26761,12 @@
       <c r="O136" t="n">
         <v>1827</v>
       </c>
+      <c r="R136" t="n">
+        <v>9.307182883341824</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -26945,9 +27149,12 @@
       <c r="O138" t="n">
         <v>378</v>
       </c>
+      <c r="R138" t="n">
+        <v>1.925624044829343</v>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -27330,9 +27537,12 @@
       <c r="O140" t="n">
         <v>10</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.05094243504839531</v>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -27715,9 +27925,12 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
+      <c r="R142" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -28100,9 +28313,12 @@
       <c r="O144" t="n">
         <v>18</v>
       </c>
+      <c r="R144" t="n">
+        <v>0.09169638308711156</v>
+      </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -28485,9 +28701,12 @@
       <c r="O146" t="n">
         <v>171</v>
       </c>
+      <c r="R146" t="n">
+        <v>0.8711156393275599</v>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -28870,9 +29089,12 @@
       <c r="O148" t="n">
         <v>194</v>
       </c>
+      <c r="R148" t="n">
+        <v>0.9882832399388691</v>
+      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -29255,9 +29477,12 @@
       <c r="O150" t="n">
         <v>1618</v>
       </c>
+      <c r="R150" t="n">
+        <v>8.242485990830362</v>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -29640,9 +29865,12 @@
       <c r="O152" t="n">
         <v>90</v>
       </c>
+      <c r="R152" t="n">
+        <v>0.4584819154355578</v>
+      </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -30025,9 +30253,12 @@
       <c r="O154" t="n">
         <v>17</v>
       </c>
+      <c r="R154" t="n">
+        <v>0.08660213958227203</v>
+      </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -30410,9 +30641,12 @@
       <c r="O156" t="n">
         <v>1834</v>
       </c>
+      <c r="R156" t="n">
+        <v>9.342842587875701</v>
+      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -30795,9 +31029,12 @@
       <c r="O158" t="n">
         <v>2537</v>
       </c>
+      <c r="R158" t="n">
+        <v>12.92409577177789</v>
+      </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -31180,9 +31417,12 @@
       <c r="O160" t="n">
         <v>76</v>
       </c>
+      <c r="R160" t="n">
+        <v>0.3871625063678044</v>
+      </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -31565,9 +31805,12 @@
       <c r="O162" t="n">
         <v>150</v>
       </c>
+      <c r="R162" t="n">
+        <v>0.7641365257259297</v>
+      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -31950,9 +32193,12 @@
       <c r="O164" t="n">
         <v>59</v>
       </c>
+      <c r="R164" t="n">
+        <v>0.3005603667855324</v>
+      </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -32335,9 +32581,12 @@
       <c r="O166" t="n">
         <v>52</v>
       </c>
+      <c r="R166" t="n">
+        <v>0.2649006622516556</v>
+      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -32720,9 +32969,12 @@
       <c r="O168" t="n">
         <v>276</v>
       </c>
+      <c r="R168" t="n">
+        <v>1.406011207335711</v>
+      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -33105,9 +33357,12 @@
       <c r="O170" t="n">
         <v>101</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.5145185939887926</v>
+      </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -33490,9 +33745,12 @@
       <c r="O172" t="n">
         <v>3</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.01528273051451859</v>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -33875,9 +34133,12 @@
       <c r="O174" t="n">
         <v>1079</v>
       </c>
+      <c r="R174" t="n">
+        <v>5.496688741721854</v>
+      </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -34260,9 +34521,12 @@
       <c r="O176" t="n">
         <v>807</v>
       </c>
+      <c r="R176" t="n">
+        <v>4.111054508405502</v>
+      </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -34645,9 +34909,12 @@
       <c r="O178" t="n">
         <v>20</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.1018848700967906</v>
+      </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -35030,9 +35297,12 @@
       <c r="O180" t="n">
         <v>18</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.09169638308711156</v>
+      </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -35415,9 +35685,12 @@
       <c r="O182" t="n">
         <v>1087</v>
       </c>
+      <c r="R182" t="n">
+        <v>5.537442689760571</v>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -35800,9 +36073,12 @@
       <c r="O184" t="n">
         <v>2</v>
       </c>
+      <c r="R184" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -36185,9 +36461,12 @@
       <c r="O186" t="n">
         <v>187</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.9526235354049923</v>
+      </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -36570,9 +36849,12 @@
       <c r="O188" t="n">
         <v>1564</v>
       </c>
+      <c r="R188" t="n">
+        <v>7.967396841569027</v>
+      </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -36955,9 +37237,12 @@
       <c r="O190" t="n">
         <v>107</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.5450840550178299</v>
+      </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -37340,9 +37625,12 @@
       <c r="O192" t="n">
         <v>18</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.09169638308711156</v>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -37725,9 +38013,12 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -38110,9 +38401,12 @@
       <c r="O196" t="n">
         <v>2740</v>
       </c>
+      <c r="R196" t="n">
+        <v>13.95822720326032</v>
+      </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -38495,9 +38789,12 @@
       <c r="O198" t="n">
         <v>2189</v>
       </c>
+      <c r="R198" t="n">
+        <v>11.15129903209373</v>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -38880,9 +39177,12 @@
       <c r="O200" t="n">
         <v>99</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.5043301069791136</v>
+      </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -39265,9 +39565,12 @@
       <c r="O202" t="n">
         <v>71</v>
       </c>
+      <c r="R202" t="n">
+        <v>0.3616912888436067</v>
+      </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -39650,9 +39953,12 @@
       <c r="O204" t="n">
         <v>44</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.2241467142129394</v>
+      </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -40035,9 +40341,12 @@
       <c r="O206" t="n">
         <v>48</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.2445236882322975</v>
+      </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -40420,9 +40729,12 @@
       <c r="O208" t="n">
         <v>333</v>
       </c>
+      <c r="R208" t="n">
+        <v>1.696383087111564</v>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -40805,9 +41117,12 @@
       <c r="O210" t="n">
         <v>109</v>
       </c>
+      <c r="R210" t="n">
+        <v>0.5552725420275089</v>
+      </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -41190,9 +41505,12 @@
       <c r="O212" t="n">
         <v>2</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -41575,9 +41893,12 @@
       <c r="O214" t="n">
         <v>1011</v>
       </c>
+      <c r="R214" t="n">
+        <v>5.150280183392766</v>
+      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -41960,9 +42281,12 @@
       <c r="O216" t="n">
         <v>492</v>
       </c>
+      <c r="R216" t="n">
+        <v>2.506367804381049</v>
+      </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -42345,9 +42669,12 @@
       <c r="O218" t="n">
         <v>21</v>
       </c>
+      <c r="R218" t="n">
+        <v>0.1069791136016301</v>
+      </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -42730,9 +43057,12 @@
       <c r="O220" t="n">
         <v>18</v>
       </c>
+      <c r="R220" t="n">
+        <v>0.09169638308711156</v>
+      </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -43115,9 +43445,12 @@
       <c r="O222" t="n">
         <v>1580</v>
       </c>
+      <c r="R222" t="n">
+        <v>8.04890473764646</v>
+      </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -43500,9 +43833,12 @@
       <c r="O224" t="n">
         <v>228</v>
       </c>
+      <c r="R224" t="n">
+        <v>1.161487519103413</v>
+      </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -43885,9 +44221,12 @@
       <c r="O226" t="n">
         <v>1536</v>
       </c>
+      <c r="R226" t="n">
+        <v>7.82475802343352</v>
+      </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -44270,9 +44609,12 @@
       <c r="O228" t="n">
         <v>92</v>
       </c>
+      <c r="R228" t="n">
+        <v>0.4686704024452369</v>
+      </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -44655,9 +44997,12 @@
       <c r="O230" t="n">
         <v>13</v>
       </c>
+      <c r="R230" t="n">
+        <v>0.06622516556291391</v>
+      </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -45040,9 +45385,12 @@
       <c r="O232" t="n">
         <v>3061</v>
       </c>
+      <c r="R232" t="n">
+        <v>15.5934793683138</v>
+      </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -45425,9 +45773,12 @@
       <c r="O234" t="n">
         <v>2025</v>
       </c>
+      <c r="R234" t="n">
+        <v>10.31584309730005</v>
+      </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -45810,9 +46161,12 @@
       <c r="O236" t="n">
         <v>99</v>
       </c>
+      <c r="R236" t="n">
+        <v>0.5043301069791136</v>
+      </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -46195,9 +46549,12 @@
       <c r="O238" t="n">
         <v>75</v>
       </c>
+      <c r="R238" t="n">
+        <v>0.3820682628629649</v>
+      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -46580,9 +46937,12 @@
       <c r="O240" t="n">
         <v>34</v>
       </c>
+      <c r="R240" t="n">
+        <v>0.1732042791645441</v>
+      </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -46965,9 +47325,12 @@
       <c r="O242" t="n">
         <v>45</v>
       </c>
+      <c r="R242" t="n">
+        <v>0.2292409577177789</v>
+      </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -47350,9 +47713,12 @@
       <c r="O244" t="n">
         <v>364</v>
       </c>
+      <c r="R244" t="n">
+        <v>1.85430463576159</v>
+      </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -47735,9 +48101,12 @@
       <c r="O246" t="n">
         <v>139</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.7080998471726949</v>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -48120,9 +48489,12 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -48505,9 +48877,12 @@
       <c r="O250" t="n">
         <v>606</v>
       </c>
+      <c r="R250" t="n">
+        <v>3.087111563932756</v>
+      </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -48890,9 +49265,12 @@
       <c r="O252" t="n">
         <v>118</v>
       </c>
+      <c r="R252" t="n">
+        <v>0.6011207335710648</v>
+      </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -49275,9 +49653,12 @@
       <c r="O254" t="n">
         <v>5</v>
       </c>
+      <c r="R254" t="n">
+        <v>0.02547121752419765</v>
+      </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -49660,9 +50041,12 @@
       <c r="O256" t="n">
         <v>15</v>
       </c>
+      <c r="R256" t="n">
+        <v>0.07641365257259297</v>
+      </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -50045,9 +50429,12 @@
       <c r="O258" t="n">
         <v>1750</v>
       </c>
+      <c r="R258" t="n">
+        <v>8.91492613346918</v>
+      </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -50430,9 +50817,12 @@
       <c r="O260" t="n">
         <v>3</v>
       </c>
+      <c r="R260" t="n">
+        <v>0.01528273051451859</v>
+      </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -50815,9 +51205,12 @@
       <c r="O262" t="n">
         <v>330</v>
       </c>
+      <c r="R262" t="n">
+        <v>1.681100356597045</v>
+      </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -51200,9 +51593,12 @@
       <c r="O264" t="n">
         <v>1790</v>
       </c>
+      <c r="R264" t="n">
+        <v>9.118695873662761</v>
+      </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -51585,9 +51981,12 @@
       <c r="O266" t="n">
         <v>97</v>
       </c>
+      <c r="R266" t="n">
+        <v>0.4941416199694346</v>
+      </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -51970,9 +52369,12 @@
       <c r="O268" t="n">
         <v>12</v>
       </c>
+      <c r="R268" t="n">
+        <v>0.06113092205807438</v>
+      </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -52355,9 +52757,12 @@
       <c r="O270" t="n">
         <v>3000</v>
       </c>
+      <c r="R270" t="n">
+        <v>15.28273051451859</v>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -52740,9 +53145,12 @@
       <c r="O272" t="n">
         <v>1938</v>
       </c>
+      <c r="R272" t="n">
+        <v>9.872643912379012</v>
+      </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -53125,9 +53533,12 @@
       <c r="O274" t="n">
         <v>174</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.8863983698420785</v>
+      </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -53510,9 +53921,12 @@
       <c r="O276" t="n">
         <v>29</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.1477330616403464</v>
+      </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -53895,9 +54309,12 @@
       <c r="O278" t="n">
         <v>27</v>
       </c>
+      <c r="R278" t="n">
+        <v>0.1375445746306674</v>
+      </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -54280,9 +54697,12 @@
       <c r="O280" t="n">
         <v>26</v>
       </c>
+      <c r="R280" t="n">
+        <v>0.1324503311258278</v>
+      </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -54665,9 +55085,12 @@
       <c r="O282" t="n">
         <v>383</v>
       </c>
+      <c r="R282" t="n">
+        <v>1.95109526235354</v>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -55050,9 +55473,12 @@
       <c r="O284" t="n">
         <v>119</v>
       </c>
+      <c r="R284" t="n">
+        <v>0.6062149770759042</v>
+      </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -55435,9 +55861,12 @@
       <c r="O286" t="n">
         <v>1</v>
       </c>
+      <c r="R286" t="n">
+        <v>0.005094243504839531</v>
+      </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -55820,9 +56249,12 @@
       <c r="O288" t="n">
         <v>329</v>
       </c>
+      <c r="R288" t="n">
+        <v>1.676006113092206</v>
+      </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -56205,9 +56637,12 @@
       <c r="O290" t="n">
         <v>23</v>
       </c>
+      <c r="R290" t="n">
+        <v>0.1171676006113092</v>
+      </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -56590,9 +57025,12 @@
       <c r="O292" t="n">
         <v>9</v>
       </c>
+      <c r="R292" t="n">
+        <v>0.04584819154355578</v>
+      </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -56975,9 +57413,12 @@
       <c r="O294" t="n">
         <v>23</v>
       </c>
+      <c r="R294" t="n">
+        <v>0.1171676006113092</v>
+      </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -57360,9 +57801,12 @@
       <c r="O296" t="n">
         <v>1913</v>
       </c>
+      <c r="R296" t="n">
+        <v>9.745287824758025</v>
+      </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -57745,9 +58189,12 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -58130,9 +58577,12 @@
       <c r="O300" t="n">
         <v>438</v>
       </c>
+      <c r="R300" t="n">
+        <v>2.231278655119715</v>
+      </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -58515,9 +58965,12 @@
       <c r="O302" t="n">
         <v>1469</v>
       </c>
+      <c r="R302" t="n">
+        <v>7.483443708609271</v>
+      </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -58900,9 +59353,12 @@
       <c r="O304" t="n">
         <v>97</v>
       </c>
+      <c r="R304" t="n">
+        <v>0.4941416199694346</v>
+      </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -59285,9 +59741,12 @@
       <c r="O306" t="n">
         <v>6</v>
       </c>
+      <c r="R306" t="n">
+        <v>0.03056546102903719</v>
+      </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -59670,9 +60129,12 @@
       <c r="O308" t="n">
         <v>1976</v>
       </c>
+      <c r="R308" t="n">
+        <v>10.06622516556291</v>
+      </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -60055,9 +60517,12 @@
       <c r="O310" t="n">
         <v>1695</v>
       </c>
+      <c r="R310" t="n">
+        <v>8.634742740703006</v>
+      </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -60440,9 +60905,12 @@
       <c r="O312" t="n">
         <v>162</v>
       </c>
+      <c r="R312" t="n">
+        <v>0.8252674477840041</v>
+      </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -60825,9 +61293,12 @@
       <c r="O314" t="n">
         <v>16</v>
       </c>
+      <c r="R314" t="n">
+        <v>0.0815078960774325</v>
+      </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -61210,9 +61681,12 @@
       <c r="O316" t="n">
         <v>22</v>
       </c>
+      <c r="R316" t="n">
+        <v>0.1120733571064697</v>
+      </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -61595,9 +62069,12 @@
       <c r="O318" t="n">
         <v>14</v>
       </c>
+      <c r="R318" t="n">
+        <v>0.07131940906775344</v>
+      </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -61980,9 +62457,12 @@
       <c r="O320" t="n">
         <v>266</v>
       </c>
+      <c r="R320" t="n">
+        <v>1.355068772287315</v>
+      </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -62365,9 +62845,12 @@
       <c r="O322" t="n">
         <v>142</v>
       </c>
+      <c r="R322" t="n">
+        <v>0.7233825776872135</v>
+      </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -62750,9 +63233,12 @@
       <c r="O324" t="n">
         <v>288</v>
       </c>
+      <c r="R324" t="n">
+        <v>1.467142129393785</v>
+      </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -63135,9 +63621,12 @@
       <c r="O326" t="n">
         <v>15</v>
       </c>
+      <c r="R326" t="n">
+        <v>0.07641365257259297</v>
+      </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -63520,9 +64009,12 @@
       <c r="O328" t="n">
         <v>5</v>
       </c>
+      <c r="R328" t="n">
+        <v>0.02547121752419765</v>
+      </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -63905,9 +64397,12 @@
       <c r="O330" t="n">
         <v>15</v>
       </c>
+      <c r="R330" t="n">
+        <v>0.07641365257259297</v>
+      </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -64290,9 +64785,12 @@
       <c r="O332" t="n">
         <v>1121</v>
       </c>
+      <c r="R332" t="n">
+        <v>5.710646968925115</v>
+      </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -64675,9 +65173,12 @@
       <c r="O334" t="n">
         <v>567</v>
       </c>
+      <c r="R334" t="n">
+        <v>2.888436067244014</v>
+      </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -65060,9 +65561,12 @@
       <c r="O336" t="n">
         <v>1446</v>
       </c>
+      <c r="R336" t="n">
+        <v>7.366276107997963</v>
+      </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -65445,9 +65949,12 @@
       <c r="O338" t="n">
         <v>105</v>
       </c>
+      <c r="R338" t="n">
+        <v>0.5348955680081507</v>
+      </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -65830,9 +66337,12 @@
       <c r="O340" t="n">
         <v>8</v>
       </c>
+      <c r="R340" t="n">
+        <v>0.04075394803871625</v>
+      </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -66215,9 +66725,12 @@
       <c r="O342" t="n">
         <v>621</v>
       </c>
+      <c r="R342" t="n">
+        <v>3.163525216505349</v>
+      </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -66600,9 +67113,12 @@
       <c r="O344" t="n">
         <v>1588</v>
       </c>
+      <c r="R344" t="n">
+        <v>8.089658685685176</v>
+      </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -66985,9 +67501,12 @@
       <c r="O346" t="n">
         <v>89</v>
       </c>
+      <c r="R346" t="n">
+        <v>0.4533876719307183</v>
+      </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -67370,9 +67889,12 @@
       <c r="O348" t="n">
         <v>11</v>
       </c>
+      <c r="R348" t="n">
+        <v>0.05603667855323484</v>
+      </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -67755,9 +68277,12 @@
       <c r="O350" t="n">
         <v>41</v>
       </c>
+      <c r="R350" t="n">
+        <v>0.2088639836984208</v>
+      </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -68140,9 +68665,12 @@
       <c r="O352" t="n">
         <v>10</v>
       </c>
+      <c r="R352" t="n">
+        <v>0.05094243504839531</v>
+      </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -68525,9 +69053,12 @@
       <c r="O354" t="n">
         <v>257</v>
       </c>
+      <c r="R354" t="n">
+        <v>1.30922058074376</v>
+      </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -68910,9 +69441,12 @@
       <c r="O356" t="n">
         <v>112</v>
       </c>
+      <c r="R356" t="n">
+        <v>0.5705552725420275</v>
+      </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -69295,9 +69829,12 @@
       <c r="O358" t="n">
         <v>559</v>
       </c>
+      <c r="R358" t="n">
+        <v>2.847682119205298</v>
+      </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -69680,9 +70217,12 @@
       <c r="O360" t="n">
         <v>13</v>
       </c>
+      <c r="R360" t="n">
+        <v>0.06622516556291391</v>
+      </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -70065,9 +70605,12 @@
       <c r="O362" t="n">
         <v>16</v>
       </c>
+      <c r="R362" t="n">
+        <v>0.0815078960774325</v>
+      </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -70450,9 +70993,12 @@
       <c r="O364" t="n">
         <v>16</v>
       </c>
+      <c r="R364" t="n">
+        <v>0.0815078960774325</v>
+      </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -70835,9 +71381,12 @@
       <c r="O366" t="n">
         <v>417</v>
       </c>
+      <c r="R366" t="n">
+        <v>2.124299541518085</v>
+      </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -71220,9 +71769,12 @@
       <c r="O368" t="n">
         <v>2</v>
       </c>
+      <c r="R368" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -71605,9 +72157,12 @@
       <c r="O370" t="n">
         <v>613</v>
       </c>
+      <c r="R370" t="n">
+        <v>3.122771268466633</v>
+      </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -71990,9 +72545,12 @@
       <c r="O372" t="n">
         <v>1347</v>
       </c>
+      <c r="R372" t="n">
+        <v>6.861946001018849</v>
+      </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -72375,9 +72933,12 @@
       <c r="O374" t="n">
         <v>113</v>
       </c>
+      <c r="R374" t="n">
+        <v>0.575649516046867</v>
+      </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -72760,9 +73321,12 @@
       <c r="O376" t="n">
         <v>10</v>
       </c>
+      <c r="R376" t="n">
+        <v>0.05094243504839531</v>
+      </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -73145,9 +73709,12 @@
       <c r="O378" t="n">
         <v>235</v>
       </c>
+      <c r="R378" t="n">
+        <v>1.19714722363729</v>
+      </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -73530,9 +74097,12 @@
       <c r="O380" t="n">
         <v>1360</v>
       </c>
+      <c r="R380" t="n">
+        <v>6.928171166581762</v>
+      </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -73915,9 +74485,12 @@
       <c r="O382" t="n">
         <v>36</v>
       </c>
+      <c r="R382" t="n">
+        <v>0.1833927661742231</v>
+      </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -74300,9 +74873,12 @@
       <c r="O384" t="n">
         <v>14</v>
       </c>
+      <c r="R384" t="n">
+        <v>0.07131940906775344</v>
+      </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -74685,9 +75261,12 @@
       <c r="O386" t="n">
         <v>76</v>
       </c>
+      <c r="R386" t="n">
+        <v>0.3871625063678044</v>
+      </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -75070,9 +75649,12 @@
       <c r="O388" t="n">
         <v>7</v>
       </c>
+      <c r="R388" t="n">
+        <v>0.03565970453387672</v>
+      </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -75455,9 +76037,12 @@
       <c r="O390" t="n">
         <v>227</v>
       </c>
+      <c r="R390" t="n">
+        <v>1.156393275598574</v>
+      </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -75840,9 +76425,12 @@
       <c r="O392" t="n">
         <v>101</v>
       </c>
+      <c r="R392" t="n">
+        <v>0.5145185939887926</v>
+      </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
@@ -76225,9 +76813,12 @@
       <c r="O394" t="n">
         <v>707</v>
       </c>
+      <c r="R394" t="n">
+        <v>3.601630157921549</v>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
@@ -76610,9 +77201,12 @@
       <c r="O396" t="n">
         <v>87</v>
       </c>
+      <c r="R396" t="n">
+        <v>0.4431991849210393</v>
+      </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
@@ -76995,9 +77589,12 @@
       <c r="O398" t="n">
         <v>11</v>
       </c>
+      <c r="R398" t="n">
+        <v>0.05603667855323484</v>
+      </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
@@ -77380,9 +77977,12 @@
       <c r="O400" t="n">
         <v>16</v>
       </c>
+      <c r="R400" t="n">
+        <v>0.0815078960774325</v>
+      </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
@@ -77765,9 +78365,12 @@
       <c r="O402" t="n">
         <v>169</v>
       </c>
+      <c r="R402" t="n">
+        <v>0.8609271523178809</v>
+      </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
@@ -78150,9 +78753,12 @@
       <c r="O404" t="n">
         <v>2</v>
       </c>
+      <c r="R404" t="n">
+        <v>0.01018848700967906</v>
+      </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
@@ -78535,9 +79141,12 @@
       <c r="O406" t="n">
         <v>450</v>
       </c>
+      <c r="R406" t="n">
+        <v>2.292409577177789</v>
+      </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
@@ -78920,9 +79529,12 @@
       <c r="O408" t="n">
         <v>1223</v>
       </c>
+      <c r="R408" t="n">
+        <v>6.230259806418746</v>
+      </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA408" t="inlineStr">
@@ -79305,9 +79917,12 @@
       <c r="O410" t="n">
         <v>96</v>
       </c>
+      <c r="R410" t="n">
+        <v>0.489047376464595</v>
+      </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA410" t="inlineStr">
@@ -79690,9 +80305,12 @@
       <c r="O412" t="n">
         <v>10</v>
       </c>
+      <c r="R412" t="n">
+        <v>0.05094243504839531</v>
+      </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA412" t="inlineStr">
@@ -80075,9 +80693,12 @@
       <c r="O414" t="n">
         <v>172</v>
       </c>
+      <c r="R414" t="n">
+        <v>0.8762098828323993</v>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -80460,9 +81081,12 @@
       <c r="O416" t="n">
         <v>1202</v>
       </c>
+      <c r="R416" t="n">
+        <v>6.123280692817117</v>
+      </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
@@ -80845,9 +81469,12 @@
       <c r="O418" t="n">
         <v>23</v>
       </c>
+      <c r="R418" t="n">
+        <v>0.1171676006113092</v>
+      </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA418" t="inlineStr">
@@ -81230,9 +81857,12 @@
       <c r="O420" t="n">
         <v>5</v>
       </c>
+      <c r="R420" t="n">
+        <v>0.02547121752419765</v>
+      </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
@@ -81615,9 +82245,12 @@
       <c r="O422" t="n">
         <v>61</v>
       </c>
+      <c r="R422" t="n">
+        <v>0.3107488537952114</v>
+      </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA422" t="inlineStr">
@@ -82000,9 +82633,12 @@
       <c r="O424" t="n">
         <v>6</v>
       </c>
+      <c r="R424" t="n">
+        <v>0.03056546102903719</v>
+      </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
@@ -82385,9 +83021,12 @@
       <c r="O426" t="n">
         <v>154</v>
       </c>
+      <c r="R426" t="n">
+        <v>0.7845134997452878</v>
+      </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA426" t="inlineStr">
@@ -82770,9 +83409,12 @@
       <c r="O428" t="n">
         <v>105</v>
       </c>
+      <c r="R428" t="n">
+        <v>0.5348955680081507</v>
+      </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA428" t="inlineStr">
@@ -83155,9 +83797,12 @@
       <c r="O430" t="n">
         <v>728</v>
       </c>
+      <c r="R430" t="n">
+        <v>3.708609271523179</v>
+      </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA430" t="inlineStr">
@@ -83540,9 +84185,12 @@
       <c r="O432" t="n">
         <v>101</v>
       </c>
+      <c r="R432" t="n">
+        <v>0.5145185939887926</v>
+      </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA432" t="inlineStr">
@@ -83925,9 +84573,12 @@
       <c r="O434" t="n">
         <v>8</v>
       </c>
+      <c r="R434" t="n">
+        <v>0.04075394803871625</v>
+      </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
@@ -84310,9 +84961,12 @@
       <c r="O436" t="n">
         <v>5</v>
       </c>
+      <c r="R436" t="n">
+        <v>0.02547121752419765</v>
+      </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA436" t="inlineStr">
@@ -84695,9 +85349,12 @@
       <c r="O438" t="n">
         <v>102</v>
       </c>
+      <c r="R438" t="n">
+        <v>0.5196128374936322</v>
+      </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AA438" t="inlineStr">
